--- a/docs/config/tbl_tenant_config 정리문서.xlsx
+++ b/docs/config/tbl_tenant_config 정리문서.xlsx
@@ -3,19 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\boh\tenant_managed_system\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="12870" yWindow="0" windowWidth="27630" windowHeight="12870"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23544" windowHeight="1728"/>
   </bookViews>
   <sheets>
     <sheet name="tbl_tenant_config" sheetId="1" r:id="rId1"/>
     <sheet name="작성일" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="539">
   <si>
     <t>LangPrimary3</t>
   </si>
@@ -106,10 +102,6 @@
   </si>
   <si>
     <t>ezTalkSyncServerUrl</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>addLastKyulJeYN</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1324,17 +1316,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>최종결재선 결재유형 허용 범위</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>전자결재 최종 결재선에서 결재유형으로 추가 할 수 있는 범위를 정한다
-0: 결재
-1: 결재+개인순차합의
-2: 결재+개인순차합의+부서순차합의</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>인접 게시글 표시</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2421,6 +2402,35 @@
   </si>
   <si>
     <t>마지막 작성일 : 2018년 09월 07일 (김보혜)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>addLastKyulJeYN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최종결재선 결재유형 허용 범위</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전자결재 최종 결재선에서 결재유형으로 추가 할 수 있는 범위를 정한다
+0: 결재
+1: 결재+개인순차합의
+2: 결재+개인순차합의+부서순차합의</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>useWebfolder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>웹폴더 기능 사용여부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>YES: 사용
+NO: 사용안함 (default)
+관리자 &gt; 권한관리 &gt; 웹폴더관리자 탭 활성화</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2837,2005 +2847,2017 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C183"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D185"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="40.625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="40.625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="100.625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="26.625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="40.59765625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="40.59765625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="100.59765625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="26.59765625" style="2" customWidth="1"/>
     <col min="5" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="54" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:3" ht="62.4" x14ac:dyDescent="0.4">
       <c r="A2" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="5" t="s">
+    </row>
+    <row r="3" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A3" s="6" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C3" s="5" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
       <c r="A4" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" s="6" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
       <c r="A6" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="5" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="62.4" x14ac:dyDescent="0.4">
+      <c r="A7" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A8" s="6" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="54" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+      <c r="B8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A9" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="54" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:3" ht="62.4" x14ac:dyDescent="0.4">
       <c r="A10" s="6" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="78" x14ac:dyDescent="0.4">
+      <c r="A11" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>524</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
-        <v>442</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>527</v>
-      </c>
       <c r="C11" s="5" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="94.5" x14ac:dyDescent="0.3">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="109.2" x14ac:dyDescent="0.4">
       <c r="A12" s="6" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="81" x14ac:dyDescent="0.3">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="93.6" x14ac:dyDescent="0.4">
       <c r="A13" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="5" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A14" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A15" s="6" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
+      <c r="B15" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A16" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A17" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B17" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
+    <row r="18" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A18" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="5" t="s">
+    </row>
+    <row r="19" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A19" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="A20" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="78" x14ac:dyDescent="0.4">
+      <c r="A21" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="A22" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="93.6" x14ac:dyDescent="0.4">
+      <c r="A23" s="6" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
+      <c r="B23" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="62.4" x14ac:dyDescent="0.4">
+      <c r="A24" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A25" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="A26" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
+      <c r="B26" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="C17" s="5" t="s">
+    </row>
+    <row r="27" spans="1:3" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="A27" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A28" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="93.6" x14ac:dyDescent="0.4">
+      <c r="A29" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A30" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A31" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A32" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A33" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="93.6" x14ac:dyDescent="0.4">
+      <c r="A34" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
-        <v>465</v>
-      </c>
-      <c r="B21" s="5" t="s">
+    <row r="35" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A35" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A36" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A37" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="A38" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="93.6" x14ac:dyDescent="0.4">
+      <c r="A39" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="A40" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A41" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A42" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A43" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="93.6" x14ac:dyDescent="0.4">
+      <c r="A44" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A45" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A46" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A47" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="78" x14ac:dyDescent="0.4">
+      <c r="A48" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A49" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="62.4" x14ac:dyDescent="0.4">
+      <c r="A50" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="78" x14ac:dyDescent="0.4">
+      <c r="A51" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A52" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="62.4" x14ac:dyDescent="0.4">
+      <c r="A53" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A54" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="A55" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="62.4" x14ac:dyDescent="0.4">
+      <c r="A56" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="A57" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A58" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="62.4" x14ac:dyDescent="0.4">
+      <c r="A59" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="78" x14ac:dyDescent="0.4">
+      <c r="A60" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A61" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="62.4" x14ac:dyDescent="0.4">
+      <c r="A62" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A63" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A64" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="62.4" x14ac:dyDescent="0.4">
+      <c r="A65" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="62.4" x14ac:dyDescent="0.4">
+      <c r="A66" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="A67" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A68" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="78" x14ac:dyDescent="0.4">
+      <c r="A69" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="62.4" x14ac:dyDescent="0.4">
+      <c r="A70" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="78" x14ac:dyDescent="0.4">
+      <c r="A71" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="62.4" x14ac:dyDescent="0.4">
+      <c r="A72" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A73" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="A74" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="109.2" x14ac:dyDescent="0.4">
+      <c r="A75" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="A76" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A77" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="78" x14ac:dyDescent="0.4">
+      <c r="A78" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="A79" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C79" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="81" x14ac:dyDescent="0.3">
-      <c r="A23" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="54" x14ac:dyDescent="0.3">
-      <c r="A24" s="6" t="s">
-        <v>443</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A25" s="6" t="s">
-        <v>404</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
-        <v>403</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A27" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A28" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="81" x14ac:dyDescent="0.3">
-      <c r="A29" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A30" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A31" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A32" s="6" t="s">
-        <v>407</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A33" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="81" x14ac:dyDescent="0.3">
-      <c r="A34" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A35" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A38" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="81" x14ac:dyDescent="0.3">
-      <c r="A39" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A40" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="6" t="s">
-        <v>411</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="C41" s="5" t="s">
+    </row>
+    <row r="80" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A80" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A81" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A82" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="A83" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A84" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A85" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A86" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="A87" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A88" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="A89" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C89" s="5" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="6" t="s">
-        <v>410</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A43" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="81" x14ac:dyDescent="0.3">
-      <c r="A44" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A45" s="6" t="s">
-        <v>448</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A46" s="6" t="s">
-        <v>413</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>414</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="A48" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A49" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="54" x14ac:dyDescent="0.3">
-      <c r="A50" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="A51" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="54" x14ac:dyDescent="0.3">
-      <c r="A53" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A54" s="6" t="s">
-        <v>447</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A55" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="54" x14ac:dyDescent="0.3">
-      <c r="A56" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A57" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A58" s="6" t="s">
-        <v>531</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>532</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="54" x14ac:dyDescent="0.3">
-      <c r="A59" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="A60" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A61" s="6" t="s">
-        <v>489</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>488</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="54" x14ac:dyDescent="0.3">
-      <c r="A62" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A63" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A64" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" ht="54" x14ac:dyDescent="0.3">
-      <c r="A65" s="6" t="s">
-        <v>418</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>416</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" ht="54" x14ac:dyDescent="0.3">
-      <c r="A66" s="6" t="s">
-        <v>419</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A67" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A68" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="A69" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" ht="54" x14ac:dyDescent="0.3">
-      <c r="A70" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="A71" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>475</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" ht="54" x14ac:dyDescent="0.3">
-      <c r="A72" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A73" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="B73" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A74" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" ht="94.5" x14ac:dyDescent="0.3">
-      <c r="A75" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A76" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A77" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="C77" s="5" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="A78" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A79" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="C79" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A80" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A82" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="C82" s="5" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A83" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A84" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A85" s="6" t="s">
-        <v>422</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>478</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A86" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A87" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A88" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A89" s="6" t="s">
+    <row r="90" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A90" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="B89" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A90" s="6" t="s">
+      <c r="B90" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="B90" s="4" t="s">
+      <c r="C90" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="C90" s="5" t="s">
+    </row>
+    <row r="91" spans="1:3" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="A91" s="6" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A91" s="6" t="s">
+      <c r="B91" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="B91" s="5" t="s">
+      <c r="C91" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="C91" s="5" t="s">
+    </row>
+    <row r="92" spans="1:3" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="A92" s="6" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A92" s="6" t="s">
+      <c r="B92" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="B92" s="4" t="s">
+      <c r="C92" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C92" s="5" t="s">
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A93" s="6" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" s="6" t="s">
+      <c r="B93" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="B93" s="4" t="s">
+      <c r="C93" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="C93" s="5" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="94" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
       <c r="A94" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B94" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C94" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="C94" s="5" t="s">
+    </row>
+    <row r="95" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A95" s="6" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A95" s="6" t="s">
+      <c r="B95" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="B95" s="4" t="s">
-        <v>190</v>
-      </c>
       <c r="C95" s="5" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
       <c r="A96" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A97" s="6" t="s">
         <v>423</v>
       </c>
-      <c r="B96" s="4" t="s">
+      <c r="B97" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="C97" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="C96" s="5" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A97" s="6" t="s">
-        <v>426</v>
-      </c>
-      <c r="B97" s="4" t="s">
-        <v>425</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" ht="54" x14ac:dyDescent="0.3">
+    </row>
+    <row r="98" spans="1:3" ht="62.4" x14ac:dyDescent="0.4">
       <c r="A98" s="6" t="s">
         <v>18</v>
       </c>
       <c r="B98" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="A99" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A100" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="C98" s="5" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A99" s="6" t="s">
+      <c r="B100" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="62.4" x14ac:dyDescent="0.4">
+      <c r="A101" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B101" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="B99" s="4" t="s">
+      <c r="C101" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="C99" s="5" t="s">
+    </row>
+    <row r="102" spans="1:3" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="A102" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A103" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="109.2" x14ac:dyDescent="0.4">
+      <c r="A104" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A105" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A106" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="A107" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" ht="93.6" x14ac:dyDescent="0.4">
+      <c r="A108" s="6" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A100" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="B100" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" ht="54" x14ac:dyDescent="0.3">
-      <c r="A101" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B101" s="4" t="s">
+      <c r="B108" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="C101" s="5" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A102" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="B102" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="C102" s="5" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A103" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="B103" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="C103" s="5" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" ht="94.5" x14ac:dyDescent="0.3">
-      <c r="A104" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="B104" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="C104" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A105" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="B105" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="C105" s="5" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A106" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="B106" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="C106" s="5" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A107" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="B107" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" ht="81" x14ac:dyDescent="0.3">
-      <c r="A108" s="6" t="s">
-        <v>433</v>
-      </c>
-      <c r="B108" s="4" t="s">
-        <v>434</v>
-      </c>
       <c r="C108" s="5" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A109" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
       <c r="A110" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B110" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A111" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A112" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A113" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="A114" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A115" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="B115" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="C110" s="5" t="s">
+      <c r="C115" s="5" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A111" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="B111" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A112" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B112" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="C112" s="5" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A113" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="B113" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="C113" s="5" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A114" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="B114" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="C114" s="5" t="s">
+    <row r="116" spans="1:3" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="A116" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="B116" s="4" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A115" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="B115" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="C115" s="5" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A116" s="6" t="s">
-        <v>485</v>
-      </c>
-      <c r="B116" s="4" t="s">
+      <c r="C116" s="5" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A117" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="C116" s="5" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A117" s="6" t="s">
+      <c r="B117" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="B117" s="4" t="s">
+      <c r="C117" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="C117" s="5" t="s">
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A118" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A119" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="B119" s="4" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A118" s="6" t="s">
-        <v>480</v>
-      </c>
-      <c r="B118" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="C118" s="5" t="s">
+      <c r="C119" s="5" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A119" s="6" t="s">
-        <v>483</v>
-      </c>
-      <c r="B119" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="C119" s="5" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A120" s="6" t="s">
         <v>6</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C120" s="5"/>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A121" s="6" t="s">
         <v>5</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="C121" s="5"/>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A122" s="6" t="s">
         <v>4</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C122" s="5"/>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A123" s="6" t="s">
         <v>3</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C123" s="5"/>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A124" s="6" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A125" s="6" t="s">
         <v>2</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C125" s="5"/>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A126" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C126" s="5"/>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A127" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C127" s="5"/>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A128" s="6" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C128" s="5"/>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A129" s="6" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" ht="31.2" x14ac:dyDescent="0.4">
       <c r="A130" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A131" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="B131" s="5" t="s">
         <v>353</v>
-      </c>
-      <c r="B130" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="C130" s="5" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A131" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="B131" s="5" t="s">
-        <v>356</v>
       </c>
       <c r="C131" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A132" s="6" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C132" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A133" s="6" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C133" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A134" s="6" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C134" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A135" s="6" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C135" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="54" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" ht="62.4" x14ac:dyDescent="0.4">
       <c r="A136" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="B136" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="B136" s="4" t="s">
+      <c r="C136" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C136" s="5" t="s">
+    </row>
+    <row r="137" spans="1:3" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="A137" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" ht="78" x14ac:dyDescent="0.4">
+      <c r="A138" s="6" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A137" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="B137" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="C137" s="5" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="A138" s="6" t="s">
+      <c r="B138" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="B138" s="5" t="s">
+      <c r="C138" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="C138" s="5" t="s">
+    </row>
+    <row r="139" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A139" s="6" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A139" s="6" t="s">
+      <c r="B139" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="C139" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="B139" s="5" t="s">
+    </row>
+    <row r="140" spans="1:3" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="A140" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="C139" s="5" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A140" s="6" t="s">
+      <c r="B140" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="B140" s="5" t="s">
+      <c r="C140" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="C140" s="5" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A141" s="6" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
       <c r="A142" s="6" t="s">
         <v>21</v>
       </c>
       <c r="B142" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C142" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="C142" s="5" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="143" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
       <c r="A143" s="6" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A144" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" ht="67.5" x14ac:dyDescent="0.3">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" ht="78" x14ac:dyDescent="0.4">
       <c r="A145" s="6" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A146" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B146" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A147" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="B147" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="C146" s="5" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A147" s="6" t="s">
+      <c r="C147" s="5" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A148" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="B147" s="4" t="s">
+      <c r="B148" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="C148" s="5" t="s">
         <v>379</v>
       </c>
-      <c r="C147" s="5" t="s">
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A149" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A150" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="C150" s="5" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A148" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="B148" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="C148" s="5" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A149" s="6" t="s">
-        <v>437</v>
-      </c>
-      <c r="B149" s="4" t="s">
-        <v>438</v>
-      </c>
-      <c r="C149" s="5" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A150" s="6" t="s">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A151" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="B150" s="4" t="s">
+      <c r="B151" s="4" t="s">
         <v>385</v>
       </c>
-      <c r="C150" s="5" t="s">
+      <c r="C151" s="5" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A151" s="6" t="s">
+    <row r="152" spans="1:3" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="A152" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C152" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="B151" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="C151" s="5" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A152" s="6" t="s">
-        <v>510</v>
-      </c>
-      <c r="B152" s="4" t="s">
-        <v>389</v>
-      </c>
-      <c r="C152" s="5" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" ht="54" x14ac:dyDescent="0.3">
+    </row>
+    <row r="153" spans="1:3" ht="62.4" x14ac:dyDescent="0.4">
       <c r="A153" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" ht="78" x14ac:dyDescent="0.4">
+      <c r="A154" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="B153" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C153" s="5" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="A154" s="6" t="s">
+      <c r="B154" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="B154" s="5" t="s">
+      <c r="C154" s="5" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A155" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="C154" s="5" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A155" s="6" t="s">
+      <c r="B155" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="B155" s="4" t="s">
+      <c r="C155" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="C155" s="5" t="s">
+    </row>
+    <row r="156" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A156" s="6" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A156" s="6" t="s">
+      <c r="B156" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="B156" s="5" t="s">
+      <c r="C156" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="C156" s="5" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A157" s="6" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C157" s="5"/>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A158" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C158" s="5" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A159" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C159" s="5" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A160" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" ht="78" x14ac:dyDescent="0.4">
+      <c r="A161" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C161" s="5" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A162" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="A163" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="C163" s="5" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A159" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="B159" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="C159" s="5" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A160" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="B160" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="C160" s="5" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="A161" s="6" t="s">
-        <v>512</v>
-      </c>
-      <c r="B161" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="C161" s="5" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A162" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="B162" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="C162" s="5" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A163" s="6" t="s">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A164" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A165" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="B165" s="5" t="s">
         <v>394</v>
-      </c>
-      <c r="B163" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="C163" s="5" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A164" s="6" t="s">
-        <v>392</v>
-      </c>
-      <c r="B164" s="4" t="s">
-        <v>393</v>
-      </c>
-      <c r="C164" s="5" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A165" s="6" t="s">
-        <v>396</v>
-      </c>
-      <c r="B165" s="5" t="s">
-        <v>397</v>
       </c>
       <c r="C165" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
       <c r="A166" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C166" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="B166" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="C166" s="5" t="s">
+    </row>
+    <row r="167" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A167" s="6" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A167" s="6" t="s">
+      <c r="B167" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C167" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="B167" s="5" t="s">
+    </row>
+    <row r="168" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A168" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="B168" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C167" s="5" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A168" s="6" t="s">
+      <c r="C168" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="B168" s="5" t="s">
+    </row>
+    <row r="169" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A169" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="C169" s="5" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" ht="62.4" x14ac:dyDescent="0.4">
+      <c r="A170" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="C170" s="5" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A171" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C171" s="5"/>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A172" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="C172" s="5"/>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A173" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C173" s="5"/>
+    </row>
+    <row r="174" spans="1:3" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A174" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="C174" s="5" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A175" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A176" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="A177" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="B177" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C168" s="5" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A169" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="B169" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="C169" s="5" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" ht="54" x14ac:dyDescent="0.3">
-      <c r="A170" s="6" t="s">
-        <v>455</v>
-      </c>
-      <c r="B170" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="C170" s="5" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A171" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="B171" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="C171" s="5"/>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A172" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="B172" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="C172" s="5"/>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A173" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="B173" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="C173" s="5"/>
-    </row>
-    <row r="174" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A174" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="B174" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="C174" s="5" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A175" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="B175" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="C175" s="5" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A176" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="B176" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="C176" s="5" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A177" s="6" t="s">
+      <c r="C177" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="B177" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C177" s="5" t="s">
+    </row>
+    <row r="178" spans="1:4" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A178" s="6" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A178" s="6" t="s">
+      <c r="B178" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="B178" s="5" t="s">
-        <v>283</v>
-      </c>
       <c r="C178" s="5" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" ht="46.8" x14ac:dyDescent="0.4">
+      <c r="A179" s="6" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="179" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A179" s="6" t="s">
+      <c r="B179" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="B179" s="5" t="s">
+      <c r="C179" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="C179" s="5" t="s">
+    </row>
+    <row r="180" spans="1:4" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="A180" s="6" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="180" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A180" s="6" t="s">
+      <c r="B180" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="B180" s="5" t="s">
+      <c r="C180" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="C180" s="5" t="s">
+    </row>
+    <row r="181" spans="1:4" ht="93.6" x14ac:dyDescent="0.4">
+      <c r="A181" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="C181" s="5" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" s="2" customFormat="1" ht="93.6" x14ac:dyDescent="0.4">
+      <c r="A182" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="B182" s="4" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="181" spans="1:3" ht="81" x14ac:dyDescent="0.3">
-      <c r="A181" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B181" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="C181" s="5" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" ht="81" x14ac:dyDescent="0.3">
-      <c r="A182" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="B182" s="4" t="s">
-        <v>295</v>
-      </c>
       <c r="C182" s="5" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" ht="54" x14ac:dyDescent="0.3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" s="2" customFormat="1" ht="62.4" x14ac:dyDescent="0.4">
       <c r="A183" s="6" t="s">
-        <v>24</v>
+        <v>533</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>293</v>
+        <v>534</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
+        <v>535</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" s="2" customFormat="1" ht="62.4" x14ac:dyDescent="0.4">
+      <c r="A184" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>537</v>
+      </c>
+      <c r="C184" s="5" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4846,18 +4868,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:D5"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="3" spans="2:4" ht="31.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:4" ht="30" x14ac:dyDescent="0.4">
       <c r="B3" s="10" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B5" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
   </sheetData>

--- a/docs/config/tbl_tenant_config 정리문서.xlsx
+++ b/docs/config/tbl_tenant_config 정리문서.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="0" windowWidth="23550" windowHeight="1725"/>
+    <workbookView xWindow="2340" yWindow="0" windowWidth="24015" windowHeight="11145"/>
   </bookViews>
   <sheets>
     <sheet name="tbl_tenant_config" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="620">
   <si>
     <t>LangPrimary3</t>
   </si>
@@ -52,9 +52,6 @@
   </si>
   <si>
     <t>청와대 게시판 모듈 호출 URL</t>
-  </si>
-  <si>
-    <t>dotNetIntegration</t>
   </si>
   <si>
     <t>코린도 아카이빙 서버 계정 생성 실패 메일 제목</t>
@@ -185,10 +182,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>printDirect</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>수신부서 표기 타입</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -250,11 +243,6 @@
   </si>
   <si>
     <t>전자설문 모듈 사용여부</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>YES: 사용 (default)
-NO: 사용안함</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -508,11 +496,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>YES: 사용
-NO: 사용안함 (default)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Use_MultiData</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -616,10 +599,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Active Directory  사용 유무</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>YES: 사용
 NO: 사용안함</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1116,10 +1095,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>YES/NO (default) *없음</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>useLoginCookieSSO</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1150,12 +1125,6 @@
   </si>
   <si>
     <t>useEncryptMailAttach</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>YES: 사용
-NO: 사용안함 (default) 
-*없음</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1190,13 +1159,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>분류코드 사용지정하고 분류코드별 문서함을 보여준다.
-1: 사용 (default)
-0: 사용안함
-*없음</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>UseBizmekaTalk</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1448,10 +1410,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>useMobileViewer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>모바일 뷰어</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1609,13 +1567,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>게시판 미리보기에서 한줄답변 리스트를 볼 수 있다.
-1: 사용
-0: 사용안함 (default)
-*없음</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>메일 이동 시 IMAP MOVE 커맨드 사용여부</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1641,10 +1592,6 @@
   </si>
   <si>
     <t>닷넷 모듈과의 연동여부</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>YES/NO</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1844,18 +1791,6 @@
     <t>채번 초기화 주기를 설정한다.
 YES: 매일 채번 초기화
 NO: 매년 채번 초기화</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>defaultForDisablePopImap</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>커뮤니티 게시판의 한줄답변 FLAG
-0: 사용안함
-1: 사용
-게시판쪽은 tbl_board_boardinfo 테이블의 onelinereply 컬럼이랑 혼용해서 사용
-(버그..? 커뮤니티 게시판에서 주석처리, 커뮤니티게시판에서 0으로 바꿔도 보임 근데 댓글입력은 빈문자로 됨)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2780,17 +2715,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>전자결재에서 모두 결재시 다음 결재문서를 보여주는 순서를 정한다. 시작하는 문서는 선택한 문서가 된다.
-Y: 기안일이 오래된 문서부터 결재
-N: 기안일이 최근인 문서부터 결재
-N의 경우에 현재 문서에서 가장 오래된 문서까지 결재하고나면 창이 닫히지 않고 오래된 기안문서부터 차례대로 나타난다. (모든 결재를 완료 할 수 있음)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>allApproveYN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">POP3/IMAP 허용 여부의 기본값을 설정한다.
 YES: 사용안함이 기본값
@@ -2872,6 +2796,156 @@
   </si>
   <si>
     <t>글자 단위로 확장자 포함한 최대 길이를 지정한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>YES</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>printDirect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dotNetIntegration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>defaultForDisablePopImap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>YES</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전자결재에서 모두 결재시 다음 결재문서를 보여주는 순서를 정한다. 시작하는 문서는 선택한 문서가 된다.
+Y: 기안일이 오래된 문서부터 결재
+N: 기안일이 최근인 문서부터 결재</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>allApproveYN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>howToSendOffer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>useApprovalKlib</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>useApprovalKlibBackup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기안자를 발송의뢰 담당자로 지정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전자결재에서 발송의뢰 할 때 심사자를 선택하는 팝업이 뜨지 않고 기안자가 바로 발송의뢰 담당자로 지정된다.
+1: 사용
+0: 사용안함 (심사자 선택)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Active Directory  사용 유무</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>useMobileViewer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게시판 미리보기에서 한줄답변 리스트를 볼 수 있다.
+1: 사용
+0: 사용안함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>YES</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>YES/NO *없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>YES: 사용
+NO: 사용안함
+*없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>YES: 사용
+NO: 사용안함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>분류코드 사용지정하고 분류코드별 문서함을 보여준다.
+1: 사용
+0: 사용안함
+*없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>커뮤니티 게시판의 한줄답변 FLAG
+0: 사용안함
+1: 사용</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2996,7 +3070,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3047,6 +3121,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3328,7 +3411,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D184"/>
+  <dimension ref="A1:D187"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.625" style="2" customWidth="1"/>
@@ -3340,1599 +3423,1639 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>24</v>
-      </c>
       <c r="D1" s="12" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="54" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>462</v>
+        <v>449</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>528</v>
+        <v>515</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" s="13"/>
     </row>
     <row r="6" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="54" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="D7" s="13"/>
+        <v>383</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>602</v>
+      </c>
     </row>
     <row r="8" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>529</v>
+        <v>516</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="54" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>530</v>
+        <v>517</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="94.5" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>579</v>
+        <v>566</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="81" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>582</v>
+        <v>569</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>531</v>
+        <v>518</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>492</v>
+        <v>479</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>532</v>
+        <v>519</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="C16" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="D16" s="13" t="s">
         <v>457</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="D17" s="13"/>
     </row>
     <row r="18" spans="1:4" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>533</v>
+        <v>520</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>510</v>
+        <v>497</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>524</v>
+        <v>511</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>580</v>
-      </c>
-      <c r="D20" s="13"/>
+        <v>567</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>610</v>
+      </c>
     </row>
     <row r="21" spans="1:4" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D22" s="13"/>
+        <v>29</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>606</v>
+      </c>
     </row>
     <row r="23" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="54" x14ac:dyDescent="0.3">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="D24" s="13"/>
+        <v>611</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>606</v>
+      </c>
     </row>
     <row r="25" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>340</v>
+        <v>609</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="D25" s="13"/>
+        <v>333</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>608</v>
+      </c>
     </row>
     <row r="26" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="D26" s="13"/>
+        <v>248</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>598</v>
+      </c>
     </row>
     <row r="27" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D28" s="13"/>
+        <v>63</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>598</v>
+      </c>
     </row>
     <row r="29" spans="1:4" ht="81" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>492</v>
+        <v>479</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>538</v>
+        <v>525</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>504</v>
+        <v>491</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="D32" s="13"/>
+        <v>336</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>612</v>
+      </c>
     </row>
     <row r="33" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="81" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>540</v>
+        <v>527</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>541</v>
+        <v>528</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>504</v>
+        <v>491</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="D37" s="13"/>
+        <v>613</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>606</v>
+      </c>
     </row>
     <row r="38" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="D38" s="13"/>
+        <v>257</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>597</v>
+      </c>
     </row>
     <row r="39" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="D41" s="13"/>
     </row>
     <row r="42" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>587</v>
+        <v>572</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>588</v>
+        <v>573</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>586</v>
+        <v>571</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>462</v>
+        <v>449</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="81" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>543</v>
+        <v>530</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="D46" s="13"/>
+        <v>342</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>602</v>
+      </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="D47" s="13"/>
     </row>
     <row r="48" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="D49" s="13"/>
+        <v>614</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>610</v>
+      </c>
     </row>
     <row r="50" spans="1:4" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>545</v>
+        <v>532</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>509</v>
+        <v>496</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="D51" s="13"/>
+        <v>266</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>598</v>
+      </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="D52" s="13"/>
     </row>
     <row r="53" spans="1:4" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>546</v>
+        <v>533</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
-        <v>589</v>
+        <v>574</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D55" s="13"/>
+        <v>615</v>
+      </c>
+      <c r="D55" s="13" t="s">
+        <v>612</v>
+      </c>
     </row>
     <row r="56" spans="1:4" ht="54" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>547</v>
+        <v>534</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>504</v>
+        <v>491</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>548</v>
+        <v>535</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>510</v>
+        <v>497</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="54" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="D59" s="13"/>
+        <v>617</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>616</v>
+      </c>
     </row>
     <row r="60" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>549</v>
+        <v>536</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>510</v>
+        <v>497</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>550</v>
+        <v>537</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>551</v>
+        <v>538</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="54" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="54" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>553</v>
+        <v>540</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>504</v>
+        <v>491</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>555</v>
+        <v>542</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="81" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>556</v>
+        <v>543</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
-        <v>590</v>
+        <v>575</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>557</v>
+        <v>544</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>558</v>
+        <v>545</v>
       </c>
       <c r="D73" s="13" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>559</v>
+        <v>546</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="94.5" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>560</v>
+        <v>547</v>
       </c>
       <c r="D75" s="13" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>561</v>
-      </c>
-      <c r="D77" s="13"/>
+        <v>548</v>
+      </c>
+      <c r="D77" s="13" t="s">
+        <v>602</v>
+      </c>
     </row>
     <row r="78" spans="1:4" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
-        <v>591</v>
+        <v>576</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D79" s="13" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>562</v>
+        <v>549</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="D81" s="13"/>
+        <v>244</v>
+      </c>
+      <c r="D81" s="13" t="s">
+        <v>606</v>
+      </c>
     </row>
     <row r="82" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A82" s="6" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>563</v>
+        <v>550</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>505</v>
+        <v>492</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A83" s="6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="D83" s="13" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
-        <v>592</v>
+        <v>577</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="D84" s="13" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="D85" s="13" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D86" s="13" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A87" s="6" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="D87" s="13" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A88" s="6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="D88" s="13" t="s">
-        <v>494</v>
+        <v>481</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="D89" s="13" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A90" s="6" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D90" s="13" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>143</v>
+        <v>607</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D91" s="13"/>
+        <v>139</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>606</v>
+      </c>
     </row>
     <row r="92" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D92" s="13" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="6" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D93" s="13" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A94" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D94" s="13" t="s">
-        <v>511</v>
+        <v>498</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="54" x14ac:dyDescent="0.3">
       <c r="A95" s="6" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>564</v>
+        <v>551</v>
       </c>
       <c r="D95" s="13" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A96" s="6" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="D96" s="13" t="s">
-        <v>499</v>
+        <v>486</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A97" s="6" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="D97" s="13"/>
+        <v>352</v>
+      </c>
+      <c r="D97" s="13" t="s">
+        <v>618</v>
+      </c>
     </row>
     <row r="98" spans="1:4" ht="54" x14ac:dyDescent="0.3">
       <c r="A98" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>438</v>
-      </c>
-      <c r="D98" s="13"/>
+        <v>425</v>
+      </c>
+      <c r="D98" s="13" t="s">
+        <v>586</v>
+      </c>
     </row>
     <row r="99" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A99" s="6" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="D99" s="13"/>
     </row>
     <row r="100" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A100" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="D100" s="13" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="54" x14ac:dyDescent="0.3">
       <c r="A101" s="6" t="s">
-        <v>42</v>
+        <v>587</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="D101" s="13"/>
     </row>
     <row r="102" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A102" s="6" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D102" s="13" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A103" s="6" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="D103" s="13" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="94.5" x14ac:dyDescent="0.3">
       <c r="A104" s="6" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>581</v>
+        <v>568</v>
       </c>
       <c r="D104" s="13" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A105" s="6" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D105" s="13" t="s">
-        <v>517</v>
+        <v>504</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="6" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="D106" s="13"/>
     </row>
     <row r="107" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A107" s="6" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="D107" s="13"/>
     </row>
-    <row r="108" spans="1:4" ht="81" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A108" s="6" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>433</v>
+        <v>619</v>
       </c>
       <c r="D108" s="13" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="D109" s="13"/>
     </row>
     <row r="110" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A110" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="D110" s="13"/>
     </row>
     <row r="111" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A111" s="6" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="D111" s="13" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A112" s="6" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>567</v>
+        <v>554</v>
       </c>
       <c r="D112" s="13" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A113" s="6" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="D113" s="13" t="s">
-        <v>503</v>
+        <v>490</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A114" s="6" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D114" s="13" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="6" t="s">
-        <v>593</v>
+        <v>578</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="D115" s="13"/>
     </row>
     <row r="116" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A116" s="6" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="D116" s="13"/>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="6" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D117" s="13" t="s">
-        <v>486</v>
+        <v>473</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="6" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>568</v>
+        <v>555</v>
       </c>
       <c r="D118" s="13" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="6" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="D119" s="13"/>
     </row>
@@ -4941,7 +5064,7 @@
         <v>6</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="C120" s="5"/>
       <c r="D120" s="13"/>
@@ -4951,11 +5074,11 @@
         <v>5</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="C121" s="5"/>
       <c r="D121" s="13" t="s">
-        <v>485</v>
+        <v>472</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
@@ -4963,11 +5086,11 @@
         <v>4</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="C122" s="5"/>
       <c r="D122" s="13" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
@@ -4975,25 +5098,25 @@
         <v>3</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="C123" s="5"/>
       <c r="D123" s="13" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="6" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="D124" s="13" t="s">
-        <v>482</v>
+        <v>469</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
@@ -5001,7 +5124,7 @@
         <v>2</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="C125" s="5"/>
       <c r="D125" s="13"/>
@@ -5011,11 +5134,11 @@
         <v>1</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="C126" s="5"/>
       <c r="D126" s="15" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
@@ -5023,346 +5146,350 @@
         <v>0</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="C127" s="5"/>
       <c r="D127" s="13" t="s">
-        <v>480</v>
+        <v>467</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" s="6" t="s">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="C128" s="5"/>
       <c r="D128" s="13" t="s">
-        <v>479</v>
+        <v>466</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" s="6" t="s">
-        <v>594</v>
+        <v>579</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="D129" s="13" t="s">
-        <v>478</v>
+        <v>465</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A130" s="6" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="D130" s="13"/>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="6" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D131" s="13"/>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" s="6" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D132" s="13"/>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" s="6" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D133" s="13"/>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" s="6" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D134" s="13"/>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" s="6" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D135" s="13"/>
     </row>
     <row r="136" spans="1:4" ht="54" x14ac:dyDescent="0.3">
       <c r="A136" s="6" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D136" s="13" t="s">
-        <v>501</v>
+        <v>488</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A137" s="6" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>569</v>
+        <v>556</v>
       </c>
       <c r="D137" s="13"/>
     </row>
     <row r="138" spans="1:4" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A138" s="6" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>570</v>
+        <v>557</v>
       </c>
       <c r="D138" s="13" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A139" s="6" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D139" s="13" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A140" s="6" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D140" s="13" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" s="6" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D141" s="13" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A142" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="D142" s="13"/>
+        <v>187</v>
+      </c>
+      <c r="D142" s="13" t="s">
+        <v>588</v>
+      </c>
     </row>
     <row r="143" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A143" s="6" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="D143" s="13" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A144" s="6" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="B144" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="D144" s="13" t="s">
         <v>454</v>
-      </c>
-      <c r="C144" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="D144" s="13" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A145" s="6" t="s">
-        <v>595</v>
+        <v>580</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="D145" s="13" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" s="6" t="s">
-        <v>597</v>
+        <v>582</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>596</v>
+        <v>581</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="D146" s="16" t="s">
-        <v>526</v>
+        <v>513</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" s="6" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="D147" s="13" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" s="6" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="D148" s="13" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" s="6" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="D149" s="13"/>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" s="6" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>598</v>
+        <v>583</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="D150" s="13"/>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" s="6" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="D151" s="13"/>
     </row>
     <row r="152" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A152" s="6" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="D152" s="13"/>
+        <v>321</v>
+      </c>
+      <c r="D152" s="13" t="s">
+        <v>589</v>
+      </c>
     </row>
     <row r="153" spans="1:4" ht="54" x14ac:dyDescent="0.3">
       <c r="A153" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="D153" s="13">
         <v>0</v>
@@ -5370,150 +5497,154 @@
     </row>
     <row r="154" spans="1:4" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A154" s="6" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="D154" s="13" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" s="6" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D155" s="13" t="s">
-        <v>474</v>
+        <v>461</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A156" s="6" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="D156" s="13" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" s="6" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="C157" s="5"/>
       <c r="D157" s="13"/>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A158" s="6" t="s">
-        <v>8</v>
+        <v>590</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="D158" s="13"/>
+        <v>321</v>
+      </c>
+      <c r="D158" s="13" t="s">
+        <v>591</v>
+      </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" s="6" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D159" s="13"/>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" s="6" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D160" s="13" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="81" x14ac:dyDescent="0.3">
       <c r="A161" s="6" t="s">
-        <v>432</v>
+        <v>592</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>585</v>
-      </c>
-      <c r="D161" s="13"/>
+        <v>570</v>
+      </c>
+      <c r="D161" s="13" t="s">
+        <v>593</v>
+      </c>
     </row>
     <row r="162" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A162" s="6" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="D162" s="13" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A163" s="6" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="D163" s="13"/>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" s="6" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="D164" s="13"/>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" s="6" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="C165" s="5" t="s">
         <v>7</v>
@@ -5522,227 +5653,229 @@
     </row>
     <row r="166" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A166" s="6" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="D166" s="13" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A167" s="6" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D167" s="13" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A168" s="6" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D168" s="13" t="s">
-        <v>501</v>
+        <v>488</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A169" s="6" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D169" s="13" t="s">
-        <v>504</v>
+        <v>491</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="54" x14ac:dyDescent="0.3">
       <c r="A170" s="6" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>574</v>
+        <v>561</v>
       </c>
       <c r="D170" s="13"/>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" s="6" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C171" s="5"/>
       <c r="D171" s="13" t="s">
-        <v>508</v>
+        <v>495</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" s="6" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C172" s="5"/>
       <c r="D172" s="13" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" s="6" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C173" s="5"/>
       <c r="D173" s="13" t="s">
-        <v>506</v>
+        <v>493</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A174" s="6" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="D174" s="13" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" s="6" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D175" s="13" t="s">
-        <v>471</v>
+        <v>458</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" s="6" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="D176" s="13" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A177" s="6" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="D177" s="13" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A178" s="6" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D178" s="13" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A179" s="6" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>575</v>
+        <v>562</v>
       </c>
       <c r="D179" s="13" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A180" s="6" t="s">
-        <v>599</v>
+        <v>584</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D180" s="13" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" ht="81" x14ac:dyDescent="0.3">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A181" s="6" t="s">
-        <v>584</v>
+        <v>595</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>583</v>
-      </c>
-      <c r="D181" s="13"/>
+        <v>594</v>
+      </c>
+      <c r="D181" s="13" t="s">
+        <v>596</v>
+      </c>
     </row>
     <row r="182" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A182" s="6" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="D182" s="13">
         <v>1</v>
@@ -5750,31 +5883,61 @@
     </row>
     <row r="183" spans="1:4" ht="54" x14ac:dyDescent="0.3">
       <c r="A183" s="6" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="D183" s="13" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="54" x14ac:dyDescent="0.3">
       <c r="A184" s="6" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="D184" s="13" t="s">
-        <v>497</v>
-      </c>
+        <v>484</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A185" s="17" t="s">
+        <v>599</v>
+      </c>
+      <c r="B185" s="18" t="s">
+        <v>604</v>
+      </c>
+      <c r="C185" s="19" t="s">
+        <v>605</v>
+      </c>
+      <c r="D185" s="13" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A186" s="17" t="s">
+        <v>600</v>
+      </c>
+      <c r="B186" s="18"/>
+      <c r="C186" s="19"/>
+      <c r="D186" s="13"/>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A187" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="B187" s="18"/>
+      <c r="C187" s="19"/>
+      <c r="D187" s="13"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D184"/>
@@ -5791,14 +5954,14 @@
   <sheetData>
     <row r="3" spans="2:4" ht="31.5" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
     </row>
   </sheetData>

--- a/docs/config/tbl_tenant_config 정리문서.xlsx
+++ b/docs/config/tbl_tenant_config 정리문서.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NC383\eGovFrameDev\workspace\ezFlow4Java\docs\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workspace\ezFlow4Java\docs\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="624">
   <si>
     <t>LangPrimary3</t>
   </si>
@@ -2946,6 +2946,23 @@
     <t>커뮤니티 게시판의 한줄답변 FLAG
 0: 사용안함
 1: 사용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>USE_ezPMS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로젝트관리 기능 사용 여부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>YES : 사용
+NO : 사용안함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NO</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3070,7 +3087,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3130,6 +3147,9 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3411,7 +3431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D187"/>
+  <dimension ref="A1:D188"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.625" style="2" customWidth="1"/>
@@ -5938,6 +5958,20 @@
       <c r="B187" s="18"/>
       <c r="C187" s="19"/>
       <c r="D187" s="13"/>
+    </row>
+    <row r="188" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A188" s="20" t="s">
+        <v>620</v>
+      </c>
+      <c r="B188" s="18" t="s">
+        <v>621</v>
+      </c>
+      <c r="C188" s="19" t="s">
+        <v>622</v>
+      </c>
+      <c r="D188" s="13" t="s">
+        <v>623</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D184"/>

--- a/docs/config/tbl_tenant_config 정리문서.xlsx
+++ b/docs/config/tbl_tenant_config 정리문서.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workspace\ezFlow4Java\docs\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NC383\eGovFrameDev\workspace\ezFlow4Java\docs\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="0" windowWidth="24015" windowHeight="11145"/>
+    <workbookView xWindow="3510" yWindow="0" windowWidth="24015" windowHeight="11145"/>
   </bookViews>
   <sheets>
     <sheet name="tbl_tenant_config" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="626">
   <si>
     <t>LangPrimary3</t>
   </si>
@@ -2957,13 +2957,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>NO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>USE_COMMUNITY</t>
+  </si>
+  <si>
     <t>YES : 사용
 NO : 사용안함</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>NO</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>커뮤니티 모듈 사용여부</t>
   </si>
 </sst>
 </file>
@@ -3431,7 +3437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D188"/>
+  <dimension ref="A1:D189"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.625" style="2" customWidth="1"/>
@@ -5967,10 +5973,24 @@
         <v>621</v>
       </c>
       <c r="C188" s="19" t="s">
+        <v>624</v>
+      </c>
+      <c r="D188" s="13" t="s">
         <v>622</v>
       </c>
-      <c r="D188" s="13" t="s">
+    </row>
+    <row r="189" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A189" s="20" t="s">
         <v>623</v>
+      </c>
+      <c r="B189" s="18" t="s">
+        <v>625</v>
+      </c>
+      <c r="C189" s="19" t="s">
+        <v>624</v>
+      </c>
+      <c r="D189" s="13" t="s">
+        <v>452</v>
       </c>
     </row>
   </sheetData>

--- a/docs/config/tbl_tenant_config 정리문서.xlsx
+++ b/docs/config/tbl_tenant_config 정리문서.xlsx
@@ -3,22 +3,18 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NC383\eGovFrameDev\workspace\ezFlow4Java\docs\config\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="0" windowWidth="24015" windowHeight="11145"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17325" windowHeight="7860"/>
   </bookViews>
   <sheets>
     <sheet name="tbl_tenant_config" sheetId="1" r:id="rId1"/>
     <sheet name="작성일" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">tbl_tenant_config!$A$1:$D$184</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">tbl_tenant_config!$A$1:$D$186</definedName>
   </definedNames>
   <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="631">
   <si>
     <t>LangPrimary3</t>
   </si>
@@ -1100,11 +1096,6 @@
   </si>
   <si>
     <t>loginCookieSSO 로그인 쿠키 추가생성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>loginCookieSSO라는 쿠키에 도메인으로 설정하여 로그인 쿠키 하나 추가로 생성
-NO: 사용안함</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2970,6 +2961,36 @@
   </si>
   <si>
     <t>커뮤니티 모듈 사용여부</t>
+  </si>
+  <si>
+    <t>useApprovalKlib</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전자결재완료 문서를 KLIB 암호화 저장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전자결재완료시 문서, 첨부파일을 KLIB 으로 암호화하여 .ezd 확장자로 저장한다.
+YES: 사용
+NO: 사용안함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전자결재완료 문서 KLIB 암호화시 원본 백업</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전자결재 관련 파일을 KLIB 으로 암호화할 때 원본 파일을 백업한다.
+YES: 사용
+NO: 사용안함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loginCookieSSO라는 쿠키에 도메인으로 설정하여 로그인 쿠키 하나 추가로 생성
+NO: 사용안함
+그 외의 값은 쿠키 도메인 값이 됨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3437,7 +3458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D189"/>
+  <dimension ref="A1:D191"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.625" style="2" customWidth="1"/>
@@ -3458,7 +3479,7 @@
         <v>23</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="54" x14ac:dyDescent="0.3">
@@ -3469,10 +3490,10 @@
         <v>44</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
@@ -3483,10 +3504,10 @@
         <v>46</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>451</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
@@ -3497,18 +3518,18 @@
         <v>24</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>381</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>382</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>14</v>
@@ -3523,24 +3544,24 @@
         <v>48</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="54" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>385</v>
-      </c>
       <c r="C7" s="5" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
@@ -3551,10 +3572,10 @@
         <v>25</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
@@ -3565,38 +3586,38 @@
         <v>51</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="54" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>428</v>
-      </c>
       <c r="D10" s="13" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="94.5" x14ac:dyDescent="0.3">
@@ -3604,13 +3625,13 @@
         <v>15</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="81" x14ac:dyDescent="0.3">
@@ -3621,10 +3642,10 @@
         <v>53</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -3635,10 +3656,10 @@
         <v>243</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="67.5" x14ac:dyDescent="0.3">
@@ -3649,24 +3670,24 @@
         <v>41</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>443</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>444</v>
-      </c>
       <c r="D16" s="13" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -3689,10 +3710,10 @@
         <v>42</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
@@ -3703,52 +3724,52 @@
         <v>27</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>303</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>304</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
@@ -3759,43 +3780,43 @@
         <v>57</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>368</v>
-      </c>
       <c r="C24" s="5" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B25" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>333</v>
-      </c>
       <c r="D25" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>249</v>
@@ -3804,7 +3825,7 @@
         <v>248</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="27" x14ac:dyDescent="0.3">
@@ -3818,7 +3839,7 @@
         <v>60</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
@@ -3832,7 +3853,7 @@
         <v>63</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="81" x14ac:dyDescent="0.3">
@@ -3843,10 +3864,10 @@
         <v>65</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
@@ -3857,10 +3878,10 @@
         <v>66</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
@@ -3874,21 +3895,21 @@
         <v>70</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="C32" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>336</v>
-      </c>
       <c r="D32" s="13" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
@@ -3899,10 +3920,10 @@
         <v>30</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="81" x14ac:dyDescent="0.3">
@@ -3916,7 +3937,7 @@
         <v>250</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
@@ -3927,10 +3948,10 @@
         <v>73</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
@@ -3941,10 +3962,10 @@
         <v>31</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -3955,13 +3976,13 @@
         <v>254</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>255</v>
       </c>
@@ -3969,10 +3990,10 @@
         <v>256</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>257</v>
+        <v>630</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="27" x14ac:dyDescent="0.3">
@@ -3986,7 +4007,7 @@
         <v>60</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="27" x14ac:dyDescent="0.3">
@@ -3997,36 +4018,36 @@
         <v>32</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="B41" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="B41" s="4" t="s">
-        <v>339</v>
-      </c>
       <c r="C41" s="5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D41" s="13"/>
     </row>
     <row r="42" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B42" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>572</v>
       </c>
-      <c r="C42" s="5" t="s">
-        <v>573</v>
-      </c>
       <c r="D42" s="13" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
@@ -4040,7 +4061,7 @@
         <v>79</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="81" x14ac:dyDescent="0.3">
@@ -4054,46 +4075,46 @@
         <v>83</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B46" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="C46" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="C46" s="5" t="s">
-        <v>342</v>
-      </c>
       <c r="D46" s="13" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="B47" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="B47" s="4" t="s">
-        <v>260</v>
-      </c>
       <c r="C47" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D47" s="13"/>
     </row>
@@ -4105,24 +4126,24 @@
         <v>85</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="67.5" x14ac:dyDescent="0.3">
@@ -4133,10 +4154,10 @@
         <v>33</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="67.5" x14ac:dyDescent="0.3">
@@ -4147,21 +4168,21 @@
         <v>88</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="C52" s="5" t="s">
         <v>263</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>264</v>
       </c>
       <c r="D52" s="13"/>
     </row>
@@ -4173,38 +4194,38 @@
         <v>90</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B54" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C54" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="C54" s="5" t="s">
-        <v>431</v>
-      </c>
       <c r="D54" s="13" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="54" x14ac:dyDescent="0.3">
@@ -4215,10 +4236,10 @@
         <v>92</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="27" x14ac:dyDescent="0.3">
@@ -4232,80 +4253,80 @@
         <v>94</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="B58" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="B58" s="4" t="s">
-        <v>433</v>
-      </c>
       <c r="C58" s="5" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="54" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B59" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="B59" s="4" t="s">
-        <v>269</v>
-      </c>
       <c r="C59" s="5" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="B60" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="B60" s="4" t="s">
-        <v>271</v>
-      </c>
       <c r="C60" s="5" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>95</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
         <v>99</v>
       </c>
@@ -4316,1681 +4337,1709 @@
         <v>97</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>627</v>
+      </c>
+      <c r="D64" s="13" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A65" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>629</v>
+      </c>
+      <c r="D65" s="13" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A66" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B66" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C64" s="5" t="s">
+      <c r="C66" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="D64" s="13" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="54" x14ac:dyDescent="0.3">
-      <c r="A65" s="6" t="s">
+      <c r="D66" s="13" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" s="2" customFormat="1" ht="54" x14ac:dyDescent="0.3">
+      <c r="A67" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="D67" s="13" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" s="2" customFormat="1" ht="54" x14ac:dyDescent="0.3">
+      <c r="A68" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="B65" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="C65" s="5" t="s">
+      <c r="B68" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="C68" s="5" t="s">
         <v>539</v>
       </c>
-      <c r="D65" s="13" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" ht="54" x14ac:dyDescent="0.3">
-      <c r="A66" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="C66" s="5" t="s">
+      <c r="D68" s="13" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+      <c r="A69" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C69" s="5" t="s">
         <v>540</v>
       </c>
-      <c r="D66" s="13" t="s">
+      <c r="D69" s="13" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A70" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="D70" s="13" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" s="2" customFormat="1" ht="67.5" x14ac:dyDescent="0.3">
+      <c r="A71" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D71" s="13" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+      <c r="A72" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D72" s="13" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" s="2" customFormat="1" ht="81" x14ac:dyDescent="0.3">
+      <c r="A73" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="D73" s="13" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+      <c r="A74" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="D74" s="13" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="27" x14ac:dyDescent="0.3">
-      <c r="A67" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="D67" s="13" t="s">
+    <row r="75" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A75" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>544</v>
+      </c>
+      <c r="D75" s="13" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+      <c r="A76" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" s="2" customFormat="1" ht="94.5" x14ac:dyDescent="0.3">
+      <c r="A77" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="D77" s="13" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+      <c r="A78" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="D78" s="13" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A79" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="D79" s="13" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" s="2" customFormat="1" ht="67.5" x14ac:dyDescent="0.3">
+      <c r="A80" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D80" s="13" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+      <c r="A81" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D81" s="13" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A82" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="D82" s="13" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D83" s="13" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A84" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>549</v>
+      </c>
+      <c r="D84" s="13" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A68" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="D68" s="13" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="A69" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="D69" s="13" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" ht="27" x14ac:dyDescent="0.3">
-      <c r="A70" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D70" s="13" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="81" x14ac:dyDescent="0.3">
-      <c r="A71" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>543</v>
-      </c>
-      <c r="D71" s="13" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="27" x14ac:dyDescent="0.3">
-      <c r="A72" s="6" t="s">
-        <v>575</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>544</v>
-      </c>
-      <c r="D72" s="13" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A73" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="B73" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>545</v>
-      </c>
-      <c r="D73" s="13" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="27" x14ac:dyDescent="0.3">
-      <c r="A74" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>546</v>
-      </c>
-      <c r="D74" s="13" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" ht="94.5" x14ac:dyDescent="0.3">
-      <c r="A75" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>547</v>
-      </c>
-      <c r="D75" s="13" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="27" x14ac:dyDescent="0.3">
-      <c r="A76" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="D76" s="13" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A77" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="C77" s="5" t="s">
-        <v>548</v>
-      </c>
-      <c r="D77" s="13" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="A78" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D78" s="13" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" ht="27" x14ac:dyDescent="0.3">
-      <c r="A79" s="6" t="s">
-        <v>576</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C79" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D79" s="13" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A80" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>549</v>
-      </c>
-      <c r="D80" s="13" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="D81" s="13" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A82" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C82" s="5" t="s">
-        <v>550</v>
-      </c>
-      <c r="D82" s="13" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" ht="27" x14ac:dyDescent="0.3">
-      <c r="A83" s="6" t="s">
+    <row r="85" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+      <c r="A85" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="B83" s="4" t="s">
+      <c r="B85" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C83" s="5" t="s">
-        <v>422</v>
-      </c>
-      <c r="D83" s="13" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A84" s="6" t="s">
-        <v>577</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="D84" s="13" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A85" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>390</v>
-      </c>
       <c r="C85" s="5" t="s">
-        <v>389</v>
+        <v>421</v>
       </c>
       <c r="D85" s="13" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
+        <v>576</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="D86" s="13" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A87" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="D87" s="13" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A88" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="B86" s="4" t="s">
+      <c r="B88" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C86" s="5" t="s">
+      <c r="C88" s="5" t="s">
         <v>131</v>
-      </c>
-      <c r="D86" s="13" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" ht="27" x14ac:dyDescent="0.3">
-      <c r="A87" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>503</v>
-      </c>
-      <c r="D87" s="13" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A88" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>233</v>
       </c>
       <c r="D88" s="13" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="D89" s="13" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A90" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+      <c r="A91" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="B89" s="4" t="s">
+      <c r="B91" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C89" s="5" t="s">
-        <v>424</v>
-      </c>
-      <c r="D89" s="13" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A90" s="6" t="s">
+      <c r="C91" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A92" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="B90" s="4" t="s">
+      <c r="B92" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="C90" s="5" t="s">
+      <c r="C92" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="D90" s="13" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" ht="27" x14ac:dyDescent="0.3">
-      <c r="A91" s="6" t="s">
+      <c r="D92" s="13" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+      <c r="A93" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="B91" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="C91" s="5" t="s">
+      <c r="B93" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="C93" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="D91" s="13" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" ht="27" x14ac:dyDescent="0.3">
-      <c r="A92" s="6" t="s">
+      <c r="D93" s="13" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+      <c r="A94" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="B92" s="4" t="s">
+      <c r="B94" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C92" s="5" t="s">
+      <c r="C94" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D92" s="13" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A93" s="6" t="s">
+      <c r="D94" s="13" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="B93" s="4" t="s">
+      <c r="B95" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C93" s="5" t="s">
+      <c r="C95" s="5" t="s">
         <v>145</v>
-      </c>
-      <c r="D93" s="13" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A94" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D94" s="13" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" ht="54" x14ac:dyDescent="0.3">
-      <c r="A95" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="B95" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>551</v>
       </c>
       <c r="D95" s="13" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A96" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D96" s="13" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" s="2" customFormat="1" ht="54" x14ac:dyDescent="0.3">
+      <c r="A97" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="D97" s="13" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A98" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="B98" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="B96" s="4" t="s">
+      <c r="C98" s="5" t="s">
+        <v>563</v>
+      </c>
+      <c r="D98" s="13" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A99" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="B99" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="C96" s="5" t="s">
+      <c r="C99" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="D99" s="13" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" s="2" customFormat="1" ht="54" x14ac:dyDescent="0.3">
+      <c r="A100" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="D100" s="13" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+      <c r="A101" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="D101" s="13"/>
+    </row>
+    <row r="102" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A102" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C102" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="D96" s="13" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A97" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="B97" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="D97" s="13" t="s">
+      <c r="D102" s="13" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" s="2" customFormat="1" ht="54" x14ac:dyDescent="0.3">
+      <c r="A103" s="6" t="s">
+        <v>586</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>551</v>
+      </c>
+      <c r="D103" s="13"/>
+    </row>
+    <row r="104" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+      <c r="A104" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D104" s="13" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A105" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="D105" s="13" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" s="2" customFormat="1" ht="94.5" x14ac:dyDescent="0.3">
+      <c r="A106" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>567</v>
+      </c>
+      <c r="D106" s="13" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A107" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D107" s="13" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="D108" s="13"/>
+    </row>
+    <row r="109" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+      <c r="A109" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="D109" s="13"/>
+    </row>
+    <row r="110" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A110" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C110" s="5" t="s">
         <v>618</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" ht="54" x14ac:dyDescent="0.3">
-      <c r="A98" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B98" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>425</v>
-      </c>
-      <c r="D98" s="13" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" ht="27" x14ac:dyDescent="0.3">
-      <c r="A99" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="B99" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="D99" s="13"/>
-    </row>
-    <row r="100" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A100" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B100" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>565</v>
-      </c>
-      <c r="D100" s="13" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" ht="54" x14ac:dyDescent="0.3">
-      <c r="A101" s="6" t="s">
-        <v>587</v>
-      </c>
-      <c r="B101" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="C101" s="5" t="s">
+      <c r="D110" s="13" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="D111" s="13"/>
+    </row>
+    <row r="112" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A112" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="D112" s="13"/>
+    </row>
+    <row r="113" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A113" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C113" s="5" t="s">
         <v>552</v>
       </c>
-      <c r="D101" s="13"/>
-    </row>
-    <row r="102" spans="1:4" ht="27" x14ac:dyDescent="0.3">
-      <c r="A102" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="B102" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="C102" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="D102" s="13" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A103" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="B103" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="C103" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="D103" s="13" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" ht="94.5" x14ac:dyDescent="0.3">
-      <c r="A104" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="B104" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="C104" s="5" t="s">
-        <v>568</v>
-      </c>
-      <c r="D104" s="13" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A105" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B105" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C105" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="D105" s="13" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="B106" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="C106" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="D106" s="13"/>
-    </row>
-    <row r="107" spans="1:4" ht="27" x14ac:dyDescent="0.3">
-      <c r="A107" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="B107" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="D107" s="13"/>
-    </row>
-    <row r="108" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A108" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="B108" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="C108" s="5" t="s">
-        <v>619</v>
-      </c>
-      <c r="D108" s="13" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B109" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="D109" s="13"/>
-    </row>
-    <row r="110" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A110" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B110" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="C110" s="5" t="s">
+      <c r="D113" s="13" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A114" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>553</v>
+      </c>
+      <c r="D114" s="13" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A115" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="D115" s="13" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+      <c r="A116" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D116" s="13" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="6" t="s">
+        <v>577</v>
+      </c>
+      <c r="B117" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="D110" s="13"/>
-    </row>
-    <row r="111" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A111" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="B111" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>553</v>
-      </c>
-      <c r="D111" s="13" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A112" s="6" t="s">
-        <v>447</v>
-      </c>
-      <c r="B112" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="C112" s="5" t="s">
+      <c r="C117" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="D117" s="13"/>
+    </row>
+    <row r="118" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+      <c r="A118" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D118" s="13"/>
+    </row>
+    <row r="119" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D119" s="13" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="C120" s="5" t="s">
         <v>554</v>
       </c>
-      <c r="D112" s="13" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A113" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="B113" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="C113" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="D113" s="13" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" ht="27" x14ac:dyDescent="0.3">
-      <c r="A114" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="B114" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="C114" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="D114" s="13" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115" s="6" t="s">
-        <v>578</v>
-      </c>
-      <c r="B115" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="C115" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="D115" s="13"/>
-    </row>
-    <row r="116" spans="1:4" ht="27" x14ac:dyDescent="0.3">
-      <c r="A116" s="6" t="s">
-        <v>396</v>
-      </c>
-      <c r="B116" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="C116" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="D116" s="13"/>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A117" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="B117" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="C117" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D117" s="13" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A118" s="6" t="s">
-        <v>391</v>
-      </c>
-      <c r="B118" s="4" t="s">
+      <c r="D120" s="13" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C121" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="C118" s="5" t="s">
-        <v>555</v>
-      </c>
-      <c r="D118" s="13" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A119" s="6" t="s">
-        <v>394</v>
-      </c>
-      <c r="B119" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="C119" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="D119" s="13"/>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A120" s="6" t="s">
+      <c r="D121" s="13"/>
+    </row>
+    <row r="122" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B120" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="C120" s="5"/>
-      <c r="D120" s="13"/>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A121" s="6" t="s">
+      <c r="B122" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="C122" s="5"/>
+      <c r="D122" s="13"/>
+    </row>
+    <row r="123" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B121" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="C121" s="5"/>
-      <c r="D121" s="13" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A122" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B122" s="4" t="s">
+      <c r="B123" s="4" t="s">
         <v>408</v>
-      </c>
-      <c r="C122" s="5"/>
-      <c r="D122" s="13" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A123" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B123" s="4" t="s">
-        <v>407</v>
       </c>
       <c r="C123" s="5"/>
       <c r="D123" s="13" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="C124" s="5"/>
+      <c r="D124" s="13" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A124" s="6" t="s">
+    <row r="125" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="C125" s="5"/>
+      <c r="D125" s="13" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="B126" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="B124" s="4" t="s">
-        <v>414</v>
-      </c>
-      <c r="C124" s="5" t="s">
+      <c r="C126" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="D126" s="13" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B127" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="D124" s="13" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A125" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B125" s="4" t="s">
+      <c r="C127" s="5"/>
+      <c r="D127" s="13"/>
+    </row>
+    <row r="128" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B128" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="C125" s="5"/>
-      <c r="D125" s="13"/>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A126" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B126" s="4" t="s">
+      <c r="C128" s="5"/>
+      <c r="D128" s="15" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B129" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="C126" s="5"/>
-      <c r="D126" s="15" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A127" s="6" t="s">
+      <c r="C129" s="5"/>
+      <c r="D129" s="13" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="C130" s="5"/>
+      <c r="D130" s="13" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="D131" s="13" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+      <c r="A132" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="D132" s="13"/>
+    </row>
+    <row r="133" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D133" s="13"/>
+    </row>
+    <row r="134" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D134" s="13"/>
+    </row>
+    <row r="135" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D135" s="13"/>
+    </row>
+    <row r="136" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D136" s="13"/>
+    </row>
+    <row r="137" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D137" s="13"/>
+    </row>
+    <row r="138" spans="1:4" s="2" customFormat="1" ht="54" x14ac:dyDescent="0.3">
+      <c r="A138" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D138" s="13" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+      <c r="A139" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>555</v>
+      </c>
+      <c r="D139" s="13"/>
+    </row>
+    <row r="140" spans="1:4" s="2" customFormat="1" ht="67.5" x14ac:dyDescent="0.3">
+      <c r="A140" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>556</v>
+      </c>
+      <c r="D140" s="13" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A141" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D141" s="13" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+      <c r="A142" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="D142" s="13" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="D143" s="13" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A144" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D144" s="13" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A145" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="D145" s="13" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A146" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="D146" s="13" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A147" s="6" t="s">
+        <v>579</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="D147" s="13" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D148" s="16" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="D149" s="13" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="D150" s="13" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="D151" s="13"/>
+    </row>
+    <row r="152" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="C152" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="D152" s="13"/>
+    </row>
+    <row r="153" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="D153" s="13"/>
+    </row>
+    <row r="154" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+      <c r="A154" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="C154" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="D154" s="13" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" s="2" customFormat="1" ht="54" x14ac:dyDescent="0.3">
+      <c r="A155" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C155" s="5" t="s">
+        <v>558</v>
+      </c>
+      <c r="D155" s="13">
         <v>0</v>
       </c>
-      <c r="B127" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="C127" s="5"/>
-      <c r="D127" s="13" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A128" s="6" t="s">
-        <v>411</v>
-      </c>
-      <c r="B128" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="C128" s="5"/>
-      <c r="D128" s="13" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A129" s="6" t="s">
-        <v>579</v>
-      </c>
-      <c r="B129" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="D129" s="13" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" ht="27" x14ac:dyDescent="0.3">
-      <c r="A130" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="B130" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="C130" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="D130" s="13"/>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A131" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="B131" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D131" s="13"/>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A132" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="B132" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="C132" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D132" s="13"/>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A133" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="B133" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="C133" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D133" s="13"/>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A134" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="B134" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="C134" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D134" s="13"/>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A135" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="B135" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="C135" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D135" s="13"/>
-    </row>
-    <row r="136" spans="1:4" ht="54" x14ac:dyDescent="0.3">
-      <c r="A136" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="B136" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="C136" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D136" s="13" t="s">
+    </row>
+    <row r="156" spans="1:4" s="2" customFormat="1" ht="67.5" x14ac:dyDescent="0.3">
+      <c r="A156" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="D156" s="13" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A157" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="D157" s="13" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A158" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D158" s="13" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="C159" s="5"/>
+      <c r="D159" s="13"/>
+    </row>
+    <row r="160" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+      <c r="A160" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="D160" s="13" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A161" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C161" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="D161" s="13"/>
+    </row>
+    <row r="162" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A162" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D162" s="13" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="27" x14ac:dyDescent="0.3">
-      <c r="A137" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="B137" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="C137" s="5" t="s">
-        <v>556</v>
-      </c>
-      <c r="D137" s="13"/>
-    </row>
-    <row r="138" spans="1:4" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="A138" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="B138" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="C138" s="5" t="s">
-        <v>557</v>
-      </c>
-      <c r="D138" s="13" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A139" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="B139" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="C139" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="D139" s="13" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" ht="27" x14ac:dyDescent="0.3">
-      <c r="A140" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="B140" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="C140" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="D140" s="13" t="s">
+    <row r="163" spans="1:4" s="2" customFormat="1" ht="81" x14ac:dyDescent="0.3">
+      <c r="A163" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D163" s="13" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A164" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="D164" s="13" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+      <c r="A165" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="C165" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="D165" s="13"/>
+    </row>
+    <row r="166" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="C166" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="D166" s="13"/>
+    </row>
+    <row r="167" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A167" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D167" s="13"/>
+    </row>
+    <row r="168" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A168" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="C168" s="5" t="s">
+        <v>559</v>
+      </c>
+      <c r="D168" s="13" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A169" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C169" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="D169" s="13" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A141" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="B141" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="C141" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="D141" s="13" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A142" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B142" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C142" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="D142" s="13" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A143" s="6" t="s">
-        <v>417</v>
-      </c>
-      <c r="B143" s="4" t="s">
-        <v>418</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="D143" s="13" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A144" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="B144" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="C144" s="5" t="s">
-        <v>445</v>
-      </c>
-      <c r="D144" s="13" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A145" s="6" t="s">
-        <v>580</v>
-      </c>
-      <c r="B145" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="C145" s="5" t="s">
-        <v>558</v>
-      </c>
-      <c r="D145" s="13" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A146" s="6" t="s">
-        <v>582</v>
-      </c>
-      <c r="B146" s="4" t="s">
-        <v>581</v>
-      </c>
-      <c r="C146" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="D146" s="16" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A147" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="B147" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="C147" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="D147" s="13" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A148" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="B148" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="C148" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="D148" s="13" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A149" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="B149" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="C149" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="D149" s="13"/>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A150" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="B150" s="4" t="s">
-        <v>583</v>
-      </c>
-      <c r="C150" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="D150" s="13"/>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A151" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="B151" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="C151" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="D151" s="13"/>
-    </row>
-    <row r="152" spans="1:4" ht="27" x14ac:dyDescent="0.3">
-      <c r="A152" s="6" t="s">
-        <v>419</v>
-      </c>
-      <c r="B152" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="C152" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="D152" s="13" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" ht="54" x14ac:dyDescent="0.3">
-      <c r="A153" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="B153" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C153" s="5" t="s">
-        <v>559</v>
-      </c>
-      <c r="D153" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="A154" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="B154" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C154" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="D154" s="13" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A155" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="B155" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="C155" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="D155" s="13" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A156" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="B156" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C156" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="D156" s="13" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A157" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="B157" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="C157" s="5"/>
-      <c r="D157" s="13"/>
-    </row>
-    <row r="158" spans="1:4" ht="27" x14ac:dyDescent="0.3">
-      <c r="A158" s="6" t="s">
-        <v>590</v>
-      </c>
-      <c r="B158" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="C158" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="D158" s="13" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A159" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="B159" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="C159" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D159" s="13"/>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A160" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="B160" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="C160" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="D160" s="13" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" ht="81" x14ac:dyDescent="0.3">
-      <c r="A161" s="6" t="s">
-        <v>592</v>
-      </c>
-      <c r="B161" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="C161" s="5" t="s">
-        <v>570</v>
-      </c>
-      <c r="D161" s="13" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A162" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="B162" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="C162" s="5" t="s">
-        <v>420</v>
-      </c>
-      <c r="D162" s="13" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" ht="27" x14ac:dyDescent="0.3">
-      <c r="A163" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="B163" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="C163" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="D163" s="13"/>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A164" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="B164" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="C164" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="D164" s="13"/>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A165" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="B165" s="5" t="s">
+    <row r="170" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A170" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C170" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D170" s="13" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A171" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="C171" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="D171" s="13" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" s="2" customFormat="1" ht="54" x14ac:dyDescent="0.3">
+      <c r="A172" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="B172" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="C165" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D165" s="13"/>
-    </row>
-    <row r="166" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A166" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="B166" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="C166" s="5" t="s">
+      <c r="C172" s="5" t="s">
         <v>560</v>
       </c>
-      <c r="D166" s="13" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A167" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B167" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C167" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="D167" s="13" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A168" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="B168" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C168" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="D168" s="13" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A169" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="B169" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="C169" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="D169" s="13" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" ht="54" x14ac:dyDescent="0.3">
-      <c r="A170" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="B170" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="C170" s="5" t="s">
-        <v>561</v>
-      </c>
-      <c r="D170" s="13"/>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A171" s="6" t="s">
+      <c r="D172" s="13"/>
+    </row>
+    <row r="173" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A173" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="B171" s="5" t="s">
+      <c r="B173" s="5" t="s">
         <v>220</v>
-      </c>
-      <c r="C171" s="5"/>
-      <c r="D171" s="13" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A172" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="B172" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="C172" s="5"/>
-      <c r="D172" s="13" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A173" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="B173" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="C173" s="5"/>
       <c r="D173" s="13" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A174" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C174" s="5"/>
+      <c r="D174" s="13" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="174" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A174" s="6" t="s">
+    <row r="175" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A175" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="C175" s="5"/>
+      <c r="D175" s="13" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A176" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="B174" s="4" t="s">
+      <c r="B176" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="C174" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="D174" s="13" t="s">
+      <c r="C176" s="5" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A175" s="6" t="s">
+      <c r="D176" s="13" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A177" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="B175" s="5" t="s">
+      <c r="B177" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="C175" s="5" t="s">
+      <c r="C177" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="D175" s="13" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A176" s="6" t="s">
+      <c r="D177" s="13" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A178" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="B176" s="5" t="s">
+      <c r="B178" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="C176" s="5" t="s">
-        <v>585</v>
-      </c>
-      <c r="D176" s="13" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" ht="27" x14ac:dyDescent="0.3">
-      <c r="A177" s="6" t="s">
+      <c r="C178" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="D178" s="13" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+      <c r="A179" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="B177" s="5" t="s">
+      <c r="B179" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C177" s="5" t="s">
+      <c r="C179" s="5" t="s">
         <v>230</v>
-      </c>
-      <c r="D177" s="13" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A178" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="B178" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="C178" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="D178" s="13" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A179" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="B179" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="C179" s="5" t="s">
-        <v>562</v>
       </c>
       <c r="D179" s="13" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="180" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A180" s="6" t="s">
-        <v>584</v>
+        <v>231</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D180" s="13" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="181" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A181" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="C181" s="5" t="s">
+        <v>561</v>
+      </c>
+      <c r="D181" s="13" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+      <c r="A182" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="C182" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D182" s="13" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A183" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C183" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="D183" s="13" t="s">
         <v>595</v>
       </c>
-      <c r="B181" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="C181" s="5" t="s">
-        <v>594</v>
-      </c>
-      <c r="D181" s="13" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A182" s="6" t="s">
+    </row>
+    <row r="184" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A184" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="B182" s="4" t="s">
+      <c r="B184" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="C182" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="D182" s="13">
+      <c r="C184" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="D184" s="13">
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:4" ht="54" x14ac:dyDescent="0.3">
-      <c r="A183" s="6" t="s">
+    <row r="185" spans="1:4" s="2" customFormat="1" ht="54" x14ac:dyDescent="0.3">
+      <c r="A185" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="B185" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="B183" s="4" t="s">
+      <c r="C185" s="5" t="s">
         <v>437</v>
       </c>
-      <c r="C183" s="5" t="s">
+      <c r="D185" s="13" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" s="2" customFormat="1" ht="54" x14ac:dyDescent="0.3">
+      <c r="A186" s="6" t="s">
         <v>438</v>
       </c>
-      <c r="D183" s="13" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" ht="54" x14ac:dyDescent="0.3">
-      <c r="A184" s="6" t="s">
+      <c r="B186" s="5" t="s">
         <v>439</v>
       </c>
-      <c r="B184" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="C184" s="5" t="s">
-        <v>563</v>
-      </c>
-      <c r="D184" s="13" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A185" s="17" t="s">
+      <c r="C186" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="D186" s="13" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A187" s="17" t="s">
+        <v>598</v>
+      </c>
+      <c r="B187" s="18" t="s">
+        <v>603</v>
+      </c>
+      <c r="C187" s="19" t="s">
+        <v>604</v>
+      </c>
+      <c r="D187" s="13" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A188" s="17" t="s">
         <v>599</v>
       </c>
-      <c r="B185" s="18" t="s">
-        <v>604</v>
-      </c>
-      <c r="C185" s="19" t="s">
-        <v>605</v>
-      </c>
-      <c r="D185" s="13" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A186" s="17" t="s">
+      <c r="B188" s="18"/>
+      <c r="C188" s="19"/>
+      <c r="D188" s="13"/>
+    </row>
+    <row r="189" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="17" t="s">
         <v>600</v>
       </c>
-      <c r="B186" s="18"/>
-      <c r="C186" s="19"/>
-      <c r="D186" s="13"/>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A187" s="17" t="s">
-        <v>601</v>
-      </c>
-      <c r="B187" s="18"/>
-      <c r="C187" s="19"/>
-      <c r="D187" s="13"/>
-    </row>
-    <row r="188" spans="1:4" ht="27" x14ac:dyDescent="0.3">
-      <c r="A188" s="20" t="s">
+      <c r="B189" s="18"/>
+      <c r="C189" s="19"/>
+      <c r="D189" s="13"/>
+    </row>
+    <row r="190" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+      <c r="A190" s="20" t="s">
+        <v>619</v>
+      </c>
+      <c r="B190" s="18" t="s">
         <v>620</v>
       </c>
-      <c r="B188" s="18" t="s">
+      <c r="C190" s="19" t="s">
+        <v>623</v>
+      </c>
+      <c r="D190" s="13" t="s">
         <v>621</v>
       </c>
-      <c r="C188" s="19" t="s">
+    </row>
+    <row r="191" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+      <c r="A191" s="20" t="s">
+        <v>622</v>
+      </c>
+      <c r="B191" s="18" t="s">
         <v>624</v>
       </c>
-      <c r="D188" s="13" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4" ht="27" x14ac:dyDescent="0.3">
-      <c r="A189" s="20" t="s">
+      <c r="C191" s="19" t="s">
         <v>623</v>
       </c>
-      <c r="B189" s="18" t="s">
-        <v>625</v>
-      </c>
-      <c r="C189" s="19" t="s">
-        <v>624</v>
-      </c>
-      <c r="D189" s="13" t="s">
-        <v>452</v>
+      <c r="D191" s="13" t="s">
+        <v>451</v>
       </c>
     </row>
   </sheetData>
@@ -6008,14 +6057,14 @@
   <sheetData>
     <row r="3" spans="2:4" ht="31.5" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
   </sheetData>

--- a/docs/config/tbl_tenant_config 정리문서.xlsx
+++ b/docs/config/tbl_tenant_config 정리문서.xlsx
@@ -3,6 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="164011"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DC317\git\ezFlow4Java\docs\config\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17325" windowHeight="7860"/>
   </bookViews>
@@ -14,7 +19,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">tbl_tenant_config!$A$1:$D$186</definedName>
   </definedNames>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="635">
   <si>
     <t>LangPrimary3</t>
   </si>
@@ -2990,6 +2994,23 @@
     <t>loginCookieSSO라는 쿠키에 도메인으로 설정하여 로그인 쿠키 하나 추가로 생성
 NO: 사용안함
 그 외의 값은 쿠키 도메인 값이 됨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chkSchedulePublic</t>
+  </si>
+  <si>
+    <t>일정작성시 사용자의 일정 공개 기본값 설정 기능 사용 여부 
+ON : 일정 공개/비공개 기본값 설정 기능 사용
+OFF : 일정 비공개 기본값 설정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정등록 공개범위 기본값 설정 여부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NO</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3458,7 +3479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D191"/>
+  <dimension ref="A1:D192"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.625" style="2" customWidth="1"/>
@@ -4326,7 +4347,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="63" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
         <v>99</v>
       </c>
@@ -4340,7 +4361,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="64" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
         <v>625</v>
       </c>
@@ -4354,7 +4375,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="65" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
         <v>600</v>
       </c>
@@ -4368,7 +4389,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="66" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
         <v>100</v>
       </c>
@@ -4382,7 +4403,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="67" spans="1:4" s="2" customFormat="1" ht="54" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" ht="54" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
         <v>343</v>
       </c>
@@ -4396,7 +4417,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="68" spans="1:4" s="2" customFormat="1" ht="54" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" ht="54" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
         <v>344</v>
       </c>
@@ -4410,7 +4431,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="69" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
         <v>101</v>
       </c>
@@ -4424,7 +4445,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="70" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
         <v>103</v>
       </c>
@@ -4438,7 +4459,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="71" spans="1:4" s="2" customFormat="1" ht="67.5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
         <v>105</v>
       </c>
@@ -4452,7 +4473,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="72" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
         <v>109</v>
       </c>
@@ -4466,7 +4487,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="73" spans="1:4" s="2" customFormat="1" ht="81" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" ht="81" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
         <v>387</v>
       </c>
@@ -4480,7 +4501,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="74" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
         <v>574</v>
       </c>
@@ -4494,7 +4515,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="75" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
         <v>111</v>
       </c>
@@ -4508,7 +4529,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="76" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
         <v>113</v>
       </c>
@@ -4522,7 +4543,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="77" spans="1:4" s="2" customFormat="1" ht="94.5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" ht="94.5" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
         <v>115</v>
       </c>
@@ -4536,7 +4557,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="78" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
         <v>271</v>
       </c>
@@ -4550,7 +4571,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="79" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
         <v>273</v>
       </c>
@@ -4564,7 +4585,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="80" spans="1:4" s="2" customFormat="1" ht="67.5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
         <v>117</v>
       </c>
@@ -4578,7 +4599,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="81" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
         <v>575</v>
       </c>
@@ -4592,7 +4613,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="82" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A82" s="6" t="s">
         <v>121</v>
       </c>
@@ -4606,7 +4627,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="83" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="6" t="s">
         <v>275</v>
       </c>
@@ -4620,7 +4641,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="84" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
         <v>123</v>
       </c>
@@ -4634,7 +4655,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="85" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
         <v>125</v>
       </c>
@@ -4648,7 +4669,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="86" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
         <v>576</v>
       </c>
@@ -4662,7 +4683,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="87" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A87" s="6" t="s">
         <v>346</v>
       </c>
@@ -4676,7 +4697,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="88" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A88" s="6" t="s">
         <v>129</v>
       </c>
@@ -4690,7 +4711,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="89" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
         <v>128</v>
       </c>
@@ -4704,7 +4725,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="90" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A90" s="6" t="s">
         <v>133</v>
       </c>
@@ -4718,7 +4739,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="91" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
         <v>134</v>
       </c>
@@ -4732,7 +4753,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="92" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
         <v>135</v>
       </c>
@@ -4746,7 +4767,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="93" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A93" s="6" t="s">
         <v>138</v>
       </c>
@@ -4760,7 +4781,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="94" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A94" s="6" t="s">
         <v>140</v>
       </c>
@@ -4774,7 +4795,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="95" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="6" t="s">
         <v>143</v>
       </c>
@@ -4788,7 +4809,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="96" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A96" s="6" t="s">
         <v>16</v>
       </c>
@@ -4802,7 +4823,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="97" spans="1:4" s="2" customFormat="1" ht="54" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" ht="54" x14ac:dyDescent="0.3">
       <c r="A97" s="6" t="s">
         <v>148</v>
       </c>
@@ -4816,7 +4837,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="98" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A98" s="6" t="s">
         <v>347</v>
       </c>
@@ -4830,7 +4851,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="99" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A99" s="6" t="s">
         <v>350</v>
       </c>
@@ -4844,7 +4865,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="100" spans="1:4" s="2" customFormat="1" ht="54" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" ht="54" x14ac:dyDescent="0.3">
       <c r="A100" s="6" t="s">
         <v>17</v>
       </c>
@@ -4858,7 +4879,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="101" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A101" s="6" t="s">
         <v>352</v>
       </c>
@@ -4870,7 +4891,7 @@
       </c>
       <c r="D101" s="13"/>
     </row>
-    <row r="102" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A102" s="6" t="s">
         <v>151</v>
       </c>
@@ -4884,7 +4905,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="103" spans="1:4" s="2" customFormat="1" ht="54" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" ht="54" x14ac:dyDescent="0.3">
       <c r="A103" s="6" t="s">
         <v>586</v>
       </c>
@@ -4896,7 +4917,7 @@
       </c>
       <c r="D103" s="13"/>
     </row>
-    <row r="104" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A104" s="6" t="s">
         <v>154</v>
       </c>
@@ -4910,7 +4931,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="105" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A105" s="6" t="s">
         <v>157</v>
       </c>
@@ -4924,7 +4945,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="106" spans="1:4" s="2" customFormat="1" ht="94.5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" ht="94.5" x14ac:dyDescent="0.3">
       <c r="A106" s="6" t="s">
         <v>158</v>
       </c>
@@ -4938,7 +4959,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="107" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A107" s="6" t="s">
         <v>160</v>
       </c>
@@ -4952,7 +4973,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="108" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="6" t="s">
         <v>304</v>
       </c>
@@ -4964,7 +4985,7 @@
       </c>
       <c r="D108" s="13"/>
     </row>
-    <row r="109" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A109" s="6" t="s">
         <v>278</v>
       </c>
@@ -4976,7 +4997,7 @@
       </c>
       <c r="D109" s="13"/>
     </row>
-    <row r="110" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A110" s="6" t="s">
         <v>356</v>
       </c>
@@ -4990,7 +5011,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="111" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="6" t="s">
         <v>18</v>
       </c>
@@ -5002,7 +5023,7 @@
       </c>
       <c r="D111" s="13"/>
     </row>
-    <row r="112" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A112" s="6" t="s">
         <v>19</v>
       </c>
@@ -5014,7 +5035,7 @@
       </c>
       <c r="D112" s="13"/>
     </row>
-    <row r="113" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A113" s="6" t="s">
         <v>164</v>
       </c>
@@ -5028,7 +5049,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="114" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A114" s="6" t="s">
         <v>446</v>
       </c>
@@ -5042,7 +5063,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="115" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A115" s="6" t="s">
         <v>165</v>
       </c>
@@ -5056,7 +5077,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="116" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A116" s="6" t="s">
         <v>167</v>
       </c>
@@ -5070,7 +5091,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="117" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="6" t="s">
         <v>577</v>
       </c>
@@ -5082,7 +5103,7 @@
       </c>
       <c r="D117" s="13"/>
     </row>
-    <row r="118" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A118" s="6" t="s">
         <v>395</v>
       </c>
@@ -5094,7 +5115,7 @@
       </c>
       <c r="D118" s="13"/>
     </row>
-    <row r="119" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="6" t="s">
         <v>171</v>
       </c>
@@ -5108,7 +5129,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="120" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="6" t="s">
         <v>390</v>
       </c>
@@ -5122,7 +5143,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="121" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="6" t="s">
         <v>393</v>
       </c>
@@ -5134,7 +5155,7 @@
       </c>
       <c r="D121" s="13"/>
     </row>
-    <row r="122" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="6" t="s">
         <v>6</v>
       </c>
@@ -5144,7 +5165,7 @@
       <c r="C122" s="5"/>
       <c r="D122" s="13"/>
     </row>
-    <row r="123" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="6" t="s">
         <v>5</v>
       </c>
@@ -5156,7 +5177,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="124" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="6" t="s">
         <v>4</v>
       </c>
@@ -5168,7 +5189,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="125" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="6" t="s">
         <v>3</v>
       </c>
@@ -5180,7 +5201,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="126" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="6" t="s">
         <v>412</v>
       </c>
@@ -5194,7 +5215,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="127" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="6" t="s">
         <v>2</v>
       </c>
@@ -5204,7 +5225,7 @@
       <c r="C127" s="5"/>
       <c r="D127" s="13"/>
     </row>
-    <row r="128" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" s="6" t="s">
         <v>1</v>
       </c>
@@ -5216,7 +5237,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="129" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" s="6" t="s">
         <v>0</v>
       </c>
@@ -5228,7 +5249,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="130" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" s="6" t="s">
         <v>410</v>
       </c>
@@ -5240,7 +5261,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="131" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="6" t="s">
         <v>578</v>
       </c>
@@ -5254,7 +5275,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="132" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A132" s="6" t="s">
         <v>288</v>
       </c>
@@ -5266,7 +5287,7 @@
       </c>
       <c r="D132" s="13"/>
     </row>
-    <row r="133" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" s="6" t="s">
         <v>290</v>
       </c>
@@ -5278,7 +5299,7 @@
       </c>
       <c r="D133" s="13"/>
     </row>
-    <row r="134" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" s="6" t="s">
         <v>292</v>
       </c>
@@ -5290,7 +5311,7 @@
       </c>
       <c r="D134" s="13"/>
     </row>
-    <row r="135" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" s="6" t="s">
         <v>294</v>
       </c>
@@ -5302,7 +5323,7 @@
       </c>
       <c r="D135" s="13"/>
     </row>
-    <row r="136" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" s="6" t="s">
         <v>296</v>
       </c>
@@ -5314,7 +5335,7 @@
       </c>
       <c r="D136" s="13"/>
     </row>
-    <row r="137" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" s="6" t="s">
         <v>298</v>
       </c>
@@ -5326,7 +5347,7 @@
       </c>
       <c r="D137" s="13"/>
     </row>
-    <row r="138" spans="1:4" s="2" customFormat="1" ht="54" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" ht="54" x14ac:dyDescent="0.3">
       <c r="A138" s="6" t="s">
         <v>175</v>
       </c>
@@ -5340,7 +5361,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="139" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A139" s="6" t="s">
         <v>300</v>
       </c>
@@ -5352,7 +5373,7 @@
       </c>
       <c r="D139" s="13"/>
     </row>
-    <row r="140" spans="1:4" s="2" customFormat="1" ht="67.5" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A140" s="6" t="s">
         <v>178</v>
       </c>
@@ -5366,7 +5387,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="141" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A141" s="6" t="s">
         <v>180</v>
       </c>
@@ -5380,7 +5401,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="142" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A142" s="6" t="s">
         <v>183</v>
       </c>
@@ -5394,7 +5415,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="143" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" s="6" t="s">
         <v>358</v>
       </c>
@@ -5408,7 +5429,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="144" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A144" s="6" t="s">
         <v>20</v>
       </c>
@@ -5422,7 +5443,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="145" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A145" s="6" t="s">
         <v>416</v>
       </c>
@@ -5436,7 +5457,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="146" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A146" s="6" t="s">
         <v>445</v>
       </c>
@@ -5450,7 +5471,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="147" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A147" s="6" t="s">
         <v>579</v>
       </c>
@@ -5464,7 +5485,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="148" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" s="6" t="s">
         <v>581</v>
       </c>
@@ -5478,7 +5499,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="149" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" s="6" t="s">
         <v>309</v>
       </c>
@@ -5492,7 +5513,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="150" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" s="6" t="s">
         <v>312</v>
       </c>
@@ -5506,7 +5527,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="151" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" s="6" t="s">
         <v>360</v>
       </c>
@@ -5518,7 +5539,7 @@
       </c>
       <c r="D151" s="13"/>
     </row>
-    <row r="152" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" s="6" t="s">
         <v>315</v>
       </c>
@@ -5530,7 +5551,7 @@
       </c>
       <c r="D152" s="13"/>
     </row>
-    <row r="153" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" s="6" t="s">
         <v>317</v>
       </c>
@@ -5542,7 +5563,7 @@
       </c>
       <c r="D153" s="13"/>
     </row>
-    <row r="154" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A154" s="6" t="s">
         <v>418</v>
       </c>
@@ -5556,7 +5577,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="155" spans="1:4" s="2" customFormat="1" ht="54" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" ht="54" x14ac:dyDescent="0.3">
       <c r="A155" s="6" t="s">
         <v>188</v>
       </c>
@@ -5570,7 +5591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:4" s="2" customFormat="1" ht="67.5" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A156" s="6" t="s">
         <v>189</v>
       </c>
@@ -5584,7 +5605,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="157" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" s="6" t="s">
         <v>191</v>
       </c>
@@ -5598,7 +5619,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="158" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A158" s="6" t="s">
         <v>194</v>
       </c>
@@ -5612,7 +5633,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="159" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" s="6" t="s">
         <v>375</v>
       </c>
@@ -5622,7 +5643,7 @@
       <c r="C159" s="5"/>
       <c r="D159" s="13"/>
     </row>
-    <row r="160" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A160" s="6" t="s">
         <v>589</v>
       </c>
@@ -5636,7 +5657,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="161" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" s="6" t="s">
         <v>197</v>
       </c>
@@ -5648,7 +5669,7 @@
       </c>
       <c r="D161" s="13"/>
     </row>
-    <row r="162" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" s="6" t="s">
         <v>201</v>
       </c>
@@ -5662,7 +5683,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="163" spans="1:4" s="2" customFormat="1" ht="81" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" ht="81" x14ac:dyDescent="0.3">
       <c r="A163" s="6" t="s">
         <v>591</v>
       </c>
@@ -5676,7 +5697,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="164" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A164" s="6" t="s">
         <v>204</v>
       </c>
@@ -5690,7 +5711,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="165" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A165" s="6" t="s">
         <v>324</v>
       </c>
@@ -5702,7 +5723,7 @@
       </c>
       <c r="D165" s="13"/>
     </row>
-    <row r="166" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" s="6" t="s">
         <v>322</v>
       </c>
@@ -5714,7 +5735,7 @@
       </c>
       <c r="D166" s="13"/>
     </row>
-    <row r="167" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" s="6" t="s">
         <v>326</v>
       </c>
@@ -5726,7 +5747,7 @@
       </c>
       <c r="D167" s="13"/>
     </row>
-    <row r="168" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A168" s="6" t="s">
         <v>208</v>
       </c>
@@ -5740,7 +5761,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="169" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A169" s="6" t="s">
         <v>209</v>
       </c>
@@ -5754,7 +5775,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="170" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A170" s="6" t="s">
         <v>211</v>
       </c>
@@ -5768,7 +5789,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="171" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A171" s="6" t="s">
         <v>213</v>
       </c>
@@ -5782,7 +5803,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="172" spans="1:4" s="2" customFormat="1" ht="54" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" ht="54" x14ac:dyDescent="0.3">
       <c r="A172" s="6" t="s">
         <v>372</v>
       </c>
@@ -5794,7 +5815,7 @@
       </c>
       <c r="D172" s="13"/>
     </row>
-    <row r="173" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" s="6" t="s">
         <v>221</v>
       </c>
@@ -5806,7 +5827,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="174" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" s="6" t="s">
         <v>219</v>
       </c>
@@ -5818,7 +5839,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="175" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" s="6" t="s">
         <v>218</v>
       </c>
@@ -5830,7 +5851,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="176" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A176" s="6" t="s">
         <v>222</v>
       </c>
@@ -5844,7 +5865,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="177" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177" s="6" t="s">
         <v>224</v>
       </c>
@@ -5858,7 +5879,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="178" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" s="6" t="s">
         <v>227</v>
       </c>
@@ -5872,7 +5893,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="179" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A179" s="6" t="s">
         <v>229</v>
       </c>
@@ -5886,7 +5907,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="180" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A180" s="6" t="s">
         <v>231</v>
       </c>
@@ -5900,7 +5921,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="181" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A181" s="6" t="s">
         <v>236</v>
       </c>
@@ -5914,7 +5935,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="182" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A182" s="6" t="s">
         <v>583</v>
       </c>
@@ -5928,7 +5949,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="183" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A183" s="6" t="s">
         <v>594</v>
       </c>
@@ -5942,7 +5963,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="184" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A184" s="6" t="s">
         <v>241</v>
       </c>
@@ -5956,7 +5977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:4" s="2" customFormat="1" ht="54" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" ht="54" x14ac:dyDescent="0.3">
       <c r="A185" s="6" t="s">
         <v>435</v>
       </c>
@@ -5970,7 +5991,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="186" spans="1:4" s="2" customFormat="1" ht="54" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4" ht="54" x14ac:dyDescent="0.3">
       <c r="A186" s="6" t="s">
         <v>438</v>
       </c>
@@ -5984,7 +6005,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="187" spans="1:4" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A187" s="17" t="s">
         <v>598</v>
       </c>
@@ -5998,7 +6019,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="188" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" s="17" t="s">
         <v>599</v>
       </c>
@@ -6006,7 +6027,7 @@
       <c r="C188" s="19"/>
       <c r="D188" s="13"/>
     </row>
-    <row r="189" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" s="17" t="s">
         <v>600</v>
       </c>
@@ -6014,7 +6035,7 @@
       <c r="C189" s="19"/>
       <c r="D189" s="13"/>
     </row>
-    <row r="190" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A190" s="20" t="s">
         <v>619</v>
       </c>
@@ -6028,7 +6049,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="191" spans="1:4" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A191" s="20" t="s">
         <v>622</v>
       </c>
@@ -6040,6 +6061,20 @@
       </c>
       <c r="D191" s="13" t="s">
         <v>451</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A192" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="B192" s="18" t="s">
+        <v>633</v>
+      </c>
+      <c r="C192" s="19" t="s">
+        <v>632</v>
+      </c>
+      <c r="D192" s="13" t="s">
+        <v>634</v>
       </c>
     </row>
   </sheetData>

--- a/docs/config/tbl_tenant_config 정리문서.xlsx
+++ b/docs/config/tbl_tenant_config 정리문서.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DC317\git\ezFlow4Java\docs\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\eGovFrameDev-3.5.1-64bit\workspace\ezFlow4Java\docs\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="639">
   <si>
     <t>LangPrimary3</t>
   </si>
@@ -3007,6 +3007,23 @@
   </si>
   <si>
     <t>일정등록 공개범위 기본값 설정 여부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>useCountryIP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">메일 발신국가의 국기를 표시할지 여부 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>YES : 사용
+NO : 사용안함</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3479,7 +3496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D192"/>
+  <dimension ref="A1:D193"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.625" style="2" customWidth="1"/>
@@ -6075,6 +6092,20 @@
       </c>
       <c r="D192" s="13" t="s">
         <v>634</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A193" s="20" t="s">
+        <v>635</v>
+      </c>
+      <c r="B193" s="18" t="s">
+        <v>636</v>
+      </c>
+      <c r="C193" s="19" t="s">
+        <v>637</v>
+      </c>
+      <c r="D193" s="13" t="s">
+        <v>638</v>
       </c>
     </row>
   </sheetData>

--- a/docs/config/tbl_tenant_config 정리문서.xlsx
+++ b/docs/config/tbl_tenant_config 정리문서.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="641">
   <si>
     <t>LangPrimary3</t>
   </si>
@@ -3028,6 +3028,14 @@
   </si>
   <si>
     <t>NO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>useScheduleIcs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정관리 ICS파일 가져오기 기능 사용 여부</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3496,7 +3504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D193"/>
+  <dimension ref="A1:D194"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.625" style="2" customWidth="1"/>
@@ -6106,6 +6114,20 @@
       </c>
       <c r="D193" s="13" t="s">
         <v>638</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+      <c r="A194" s="20" t="s">
+        <v>639</v>
+      </c>
+      <c r="B194" s="18" t="s">
+        <v>640</v>
+      </c>
+      <c r="C194" s="19" t="s">
+        <v>623</v>
+      </c>
+      <c r="D194" s="13" t="s">
+        <v>448</v>
       </c>
     </row>
   </sheetData>

--- a/docs/config/tbl_tenant_config 정리문서.xlsx
+++ b/docs/config/tbl_tenant_config 정리문서.xlsx
@@ -3,13 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\eGovFrameDev-3.5.1-64bit\workspace\ezFlow4Java\docs\config\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17325" windowHeight="7860"/>
+    <workbookView xWindow="1170" yWindow="0" windowWidth="21885" windowHeight="6150"/>
   </bookViews>
   <sheets>
     <sheet name="tbl_tenant_config" sheetId="1" r:id="rId1"/>
@@ -19,6 +14,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">tbl_tenant_config!$A$1:$D$186</definedName>
   </definedNames>
   <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="644">
   <si>
     <t>LangPrimary3</t>
   </si>
@@ -3037,6 +3033,15 @@
   <si>
     <t>일정관리 ICS파일 가져오기 기능 사용 여부</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>useModuleUsage</t>
+  </si>
+  <si>
+    <t>모듈별 모니터링 사용여부</t>
+  </si>
+  <si>
+    <t>관리자&gt;시스템에서 모듈별 사용량을 조회하는 모니터링 기능을 사용한다.</t>
   </si>
 </sst>
 </file>
@@ -3504,7 +3509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D194"/>
+  <dimension ref="A1:D195"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.625" style="2" customWidth="1"/>
@@ -6127,6 +6132,20 @@
         <v>623</v>
       </c>
       <c r="D194" s="13" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A195" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="B195" s="18" t="s">
+        <v>642</v>
+      </c>
+      <c r="C195" s="19" t="s">
+        <v>643</v>
+      </c>
+      <c r="D195" s="13" t="s">
         <v>448</v>
       </c>
     </row>

--- a/docs/config/tbl_tenant_config 정리문서.xlsx
+++ b/docs/config/tbl_tenant_config 정리문서.xlsx
@@ -3,6 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="164011"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ezEKP\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="1170" yWindow="0" windowWidth="21885" windowHeight="6150"/>
   </bookViews>
@@ -14,7 +19,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">tbl_tenant_config!$A$1:$D$186</definedName>
   </definedNames>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="652">
   <si>
     <t>LangPrimary3</t>
   </si>
@@ -3042,6 +3046,37 @@
   </si>
   <si>
     <t>관리자&gt;시스템에서 모듈별 사용량을 조회하는 모니터링 기능을 사용한다.</t>
+  </si>
+  <si>
+    <t>systemCountryCode</t>
+  </si>
+  <si>
+    <t>useShowSystemCountry</t>
+  </si>
+  <si>
+    <t>현재국가코드</t>
+  </si>
+  <si>
+    <t>KR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메일리스트 &gt; 국기표시시 현재국가코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>systemCountryCode와 .eml파일의 국가코드가 같을시 국기 표시할지 여부
+YES: 현재 국가도 국기표시 
+NO: 현재 국가는 표시하지 않음 (default: NO)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>systemCountryCode와 .eml파일의 국가코드가 같을시 국기 표시할지 여부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3509,7 +3544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D195"/>
+  <dimension ref="A1:D197"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.625" style="2" customWidth="1"/>
@@ -6147,6 +6182,34 @@
       </c>
       <c r="D195" s="13" t="s">
         <v>448</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A196" s="20" t="s">
+        <v>644</v>
+      </c>
+      <c r="B196" s="18" t="s">
+        <v>646</v>
+      </c>
+      <c r="C196" s="19" t="s">
+        <v>649</v>
+      </c>
+      <c r="D196" s="13" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A197" s="20" t="s">
+        <v>645</v>
+      </c>
+      <c r="B197" s="18" t="s">
+        <v>651</v>
+      </c>
+      <c r="C197" s="19" t="s">
+        <v>650</v>
+      </c>
+      <c r="D197" s="13" t="s">
+        <v>648</v>
       </c>
     </row>
   </sheetData>

--- a/docs/config/tbl_tenant_config 정리문서.xlsx
+++ b/docs/config/tbl_tenant_config 정리문서.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ezEKP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workspace\ezFlow4Java\docs\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="656">
   <si>
     <t>LangPrimary3</t>
   </si>
@@ -3076,6 +3076,21 @@
   </si>
   <si>
     <t>systemCountryCode와 .eml파일의 국가코드가 같을시 국기 표시할지 여부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mobileRedirection</t>
+  </si>
+  <si>
+    <t>모바일 기기로 접속시 리다이렉션할 주소. 단, *면 사용 안함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모바일 기기로 접속시 리다이렉션할 주소</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3544,7 +3559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D197"/>
+  <dimension ref="A1:D198"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.625" style="2" customWidth="1"/>
@@ -6210,6 +6225,20 @@
       </c>
       <c r="D197" s="13" t="s">
         <v>648</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A198" s="20" t="s">
+        <v>652</v>
+      </c>
+      <c r="B198" s="18" t="s">
+        <v>655</v>
+      </c>
+      <c r="C198" s="19" t="s">
+        <v>653</v>
+      </c>
+      <c r="D198" s="13" t="s">
+        <v>654</v>
       </c>
     </row>
   </sheetData>
